--- a/etf_holdings/2026-10-06_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-10-06_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB9"/>
+  <dimension ref="A1:BL12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,200 +489,250 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>00991A_異動類型</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>00991A_調整方向</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>00991A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>00991A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>00991A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>00991A_權重_今日</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>00991A_權重變化</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>00991A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>00991A_股數_今日</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>00991A_股數變化</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>00982A_異動類型</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>00982A_調整方向</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>00982A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>00982A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>00982A_權重_昨日</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>00982A_權重_今日</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>00982A_權重變化</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>00982A_股數_昨日</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>00982A_股數_今日</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>00982A_股數變化</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>00403A_異動類型</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>00403A_調整方向</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>00403A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>00403A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>00403A_權重_昨日</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>00403A_權重_今日</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>00403A_權重變化</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>00403A_股數_昨日</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>00403A_股數_今日</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>00403A_股數變化</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>00985A_異動類型</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>00985A_調整方向</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>00985A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>00985A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>00985A_權重_昨日</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>00985A_權重_今日</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>00985A_權重變化</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>00985A_股數_昨日</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>00985A_股數_今日</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>00985A_股數變化</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>00405A_異動類型</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>00405A_調整方向</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>00405A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>00405A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>00405A_權重_昨日</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>00405A_權重_今日</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>00405A_權重變化</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>00405A_股數_昨日</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>00405A_股數_今日</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>00405A_股數變化</t>
         </is>
@@ -700,11 +750,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00403A,00981A,00985A</t>
+          <t>00403A,00981A,00985A,00991A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -753,118 +803,164 @@
           <t>-5,000,000</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>10400000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>-10,391,000</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
         <is>
           <t>3.89%</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>2.43%</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>-1.46%</t>
         </is>
       </c>
-      <c r="AF2" t="n">
+      <c r="AP2" t="n">
         <v>38000000</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AQ2" t="n">
         <v>24000000</v>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>-14,000,000</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>2.01%</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>2.25%</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>+0.24%</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AZ2" t="n">
         <v>1648000</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="BA2" t="n">
         <v>2186000</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>538,000</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -878,11 +974,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00403A,00981A,00985A</t>
+          <t>00403A,00981A,00985A,00991A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -931,128 +1027,174 @@
           <t>-800,000</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>5280000</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>80,000</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>欣興</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>欣興</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>7.53%</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>7.00%</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>-0.53%</t>
         </is>
       </c>
-      <c r="AF3" t="n">
+      <c r="AP3" t="n">
         <v>8460000</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AQ3" t="n">
         <v>7800000</v>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>-660,000</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>欣興</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>欣興</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>1.51%</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>2.40%</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>+0.89%</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AZ3" t="n">
         <v>153000</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="BA3" t="n">
         <v>268000</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>115,000</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1060,7 +1202,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00403A,00405A,00981A</t>
+          <t>00981A,00985A,00991A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1070,101 +1212,101 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>5.16%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>4.96%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>388000</v>
+        <v>24757000</v>
       </c>
       <c r="M4" t="n">
-        <v>520000</v>
+        <v>23519000</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>132,000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3.29%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>3.56%</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>+0.27%</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>570000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>620000</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>50,000</t>
-        </is>
-      </c>
+          <t>-1,238,000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
@@ -1182,205 +1324,261 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>6.01%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>213000</v>
+        <v>492000</v>
       </c>
       <c r="BA4" t="n">
-        <v>183000</v>
+        <v>694000</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-30,000</t>
-        </is>
-      </c>
+          <t>202,000</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00981A,00985A</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+          <t>00982A,00985A,00991A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5.16%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>4.96%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-0.20%</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>24757000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>23519000</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-1,238,000</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-199,000</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>222000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>111000</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>-111,000</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>2.33%</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2.94%</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
-        </is>
-      </c>
-      <c r="AP5" t="n">
-        <v>492000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>694000</v>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>202,000</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>1.19%</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>4.57%</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>+3.38%</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>80000</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>326000</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>246,000</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00982A,00985A</t>
+          <t>00403A,00405A,00991A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -1405,38 +1603,38 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>222000</v>
+        <v>1130000</v>
       </c>
       <c r="W6" t="n">
-        <v>111000</v>
+        <v>1100000</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-111,000</t>
+          <t>-30,000</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1456,43 +1654,43 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>7.66%</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>4.57%</t>
+          <t>6.57%</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>+3.38%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>80000</v>
+        <v>2210000</v>
       </c>
       <c r="AQ6" t="n">
-        <v>326000</v>
+        <v>1950000</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>246,000</t>
+          <t>-260,000</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
@@ -1505,24 +1703,70 @@
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>6.76%</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>5.67%</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>-1.09%</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>344000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>294000</v>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>-50,000</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00403A,00981A</t>
+          <t>00403A,00405A,00981A</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1537,38 +1781,38 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2483000</v>
+        <v>388000</v>
       </c>
       <c r="M7" t="n">
-        <v>3164000</v>
+        <v>520000</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>681,000</t>
+          <t>132,000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -1581,44 +1825,62 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>0.17%</t>
-        </is>
-      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="n">
-        <v>200000</v>
-      </c>
+      <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>3.29%</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>3.56%</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>+0.27%</t>
+        </is>
+      </c>
+      <c r="AP7" t="n">
+        <v>570000</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>620000</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="inlineStr"/>
@@ -1629,16 +1891,62 @@
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>6.01%</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>-0.96%</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>213000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>183000</v>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>-30,000</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1646,7 +1954,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00403A,00405A</t>
+          <t>00403A,00991A</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1659,128 +1967,138 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>7.66%</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>6.57%</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>-1.09%</t>
-        </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>2210000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1950000</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>-260,000</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>6.76%</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>5.67%</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>-1.09%</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>344000</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>294000</v>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-50,000</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>+0.24%</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="W8" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>500,000</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>1.92%</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>2.21%</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>+0.29%</t>
+        </is>
+      </c>
+      <c r="AP8" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>1,000,000</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1788,65 +2106,65 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00405A,00981A</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+          <t>00985A,00991A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.98%</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.56%</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-0.42%</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>1204000</v>
-      </c>
-      <c r="M9" t="n">
-        <v>692000</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-512,000</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>+0.68%</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>-0.15%</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>-0.83%</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>480000</v>
+      </c>
+      <c r="W9" t="n">
+        <v>470000</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-10,000</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
@@ -1874,41 +2192,489 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.09%</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1.17%</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>+1.08%</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>13000</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>+0.35%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>2483000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3164000</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>681,000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>200000</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00985A,00991A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>+0.25%</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>-0.14%</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>-0.39%</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4620000</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>120,000</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>1.40%</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>+0.46%</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>118000</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>189000</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>71,000</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00405A,00981A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AU9" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>富世達</t>
         </is>
       </c>
-      <c r="AV9" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>富世達</t>
         </is>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>-0.42%</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1204000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>692000</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-512,000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
         <is>
           <t>3.46%</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>3.23%</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>-0.23%</t>
         </is>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BJ12" t="n">
         <v>371000</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BK12" t="n">
         <v>341000</v>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>-30,000</t>
         </is>
